--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BY2025</t>
+          <t>BY1059</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_  Efter avslutad kurs ska studenten kunna:    - redogöra för lämpliga sätt att problematisera, f…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall skaffa sig kunskaper om såväl teoretisk som praktisk träbyggnad…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1059</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BY3001</t>
+          <t>BY1061</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
+          <t>Avvikande introfras: Det övergripande målet me kursen är att studenten ska skaffa sig kunskaper och färdigheter om systemuppbyggnad och funkt…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1061</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BY3004</t>
+          <t>BY1065</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:      - Visa förståe…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att kursdeltagaren ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformati…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1065</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GBY2GB</t>
+          <t>BY2016</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.      Efter genomg…</t>
+          <t>Avvikande introfras: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GBY2GC</t>
+          <t>BY2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska uppnå förmåga att med helhetssyn självständigt och kreativt ident…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2022</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GBY2GR</t>
+          <t>BY2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_  Efter avslutad kurs ska studenten kunna:    - redogöra för lämpliga sätt att problematisera, f…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2025</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GBY2J2</t>
+          <t>BY3001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska skaffa sig kunskaper i husbyggnad, speciellt beträffande planering, utform…</t>
+          <t>Avvikande introfras: Vid design av energieffektiva byggnader med hög nivå av komfort och hållbarhet krävs både en djup kunskap om detaljer so…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2J2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3001</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GBY2MA</t>
+          <t>BY3004</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
+          <t>Avvikande introfras: Kursen fokuserar på miljöklassningsverktyg för byggnader. Efter avslutad kurs ska studenterna kunna:      - Visa förståe…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3004</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GBY2MB</t>
+          <t>BY3005</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenterna kunna:    - Ställa samman, analysera och kombinera information från olika källor för…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GBY2ME</t>
+          <t>GBY2GB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten efter genomgången kurs ska kunna rita en 3D-modell.      Efter genomg…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2ME</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GB</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GBY2NF</t>
+          <t>GBY2GC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper om BIM (Byggnadsinformationsmo…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GBY2NG</t>
+          <t>GBY2GR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig grundläggande kunskaper inom fysisk planering med tyng…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GBY2RN</t>
+          <t>GBY2J2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - redogöra för vad som styr det termiska inomhusklimatet    - redogöra…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska skaffa sig kunskaper i husbyggnad, speciellt beträffande planering, utform…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2J2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GBY2RX</t>
+          <t>GBY2MA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap och förståelse om fastighetsföretagens förutsättninga…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om laster och krafter i byggkonstruktioner…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GBY2V5</t>
+          <t>GBY2MB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - redogöra för anbuds- och produktionsprocessen     - redogöra för svensk…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper för att kunna organisera och genomföra pro…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2MB</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GBY2V6</t>
+          <t>GBY2ME</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper i husbyggnadsteknik, speciellt beträffande…</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2ME</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GBY2V8</t>
+          <t>GBY2NF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - visa förståelse för byggnadskonstruktioners funktion och säkerhet…</t>
+          <t>Avvikande introfras: Det övergripande målet är att studenten skall tillägna sig kunskaper om laster och krafter i byggkonstruktioner samt gru…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GBY2VR</t>
+          <t>GBY2NG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig kunskaper om byggandets organisation och genomförand…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2VR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GBY2XF</t>
+          <t>GBY2RN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - redogöra för vad som styr det termiska inomhusklimatet    - redogöra…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2XF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GBY33L</t>
+          <t>GBY2RX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - beskriva och utföra kulturhistorisk värdering av befintlig bebygge…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap och förståelse om fastighetsföretagens förutsättninga…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY33L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2RX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GBY34M</t>
+          <t>GBY2V5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall den studerande kunna:    - identifiera ett intressant område/ämne att undersöka och formulera e…</t>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - redogöra för anbuds- och produktionsprocessen     - redogöra för svensk…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GBY34N</t>
+          <t>GBY2V6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - identifiera ett vetenskapligt intressant område samt formulera och unders…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall tillägna sig grundläggande kunskaper i arbetsplatsens organisat…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GBY3AX</t>
+          <t>GBY2V8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:       - välja byggtekniska lösningar fö…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - visa förståelse för byggnadskonstruktioners funktion och säkerhet…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2V8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GDT2JM</t>
+          <t>GBY2VR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:      - Redogöra för historik och utveckling av system för datakommunikation s…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att öka medvetenheten om de hållbarhetsutmaningar som vi står inför. Kursen avser a…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2VR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GDT2JN</t>
+          <t>GBY2XF</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:      - Redogöra för, och värdera, hierarkiska konvergerade nätverksdesigner…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig kunskaper i husbyggnadsteknik, speciellt beträffande u…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2XF</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GDT34Z</t>
+          <t>GBY33L</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva hur teknik som virtualisering, mjukvarupaketering via containerb…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - beskriva och utföra kulturhistorisk värdering av befintlig bebygge…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY33L</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ET1029</t>
+          <t>GBY34M</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ETA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:          - Redogöra för grundläggande principer i styrteknik.    - Redogör…</t>
+          <t>Avvikande introfras: Efter godkänd kurs skall den studerande kunna:    - identifiera ett intressant område/ämne att undersöka och formulera e…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>GBY34N</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap…</t>
+          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - identifiera ett vetenskapligt intressant område samt formulera och unders…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34N</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FY1018</t>
+          <t>GBY3AX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten skall efter genomgången kurs kunna        - redogöra för termodynamikens grundbegrepp    - formulera och lösa…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande för ett konkret husbyggnadsprojekt kunna:       - välja byggtekniska lösningar fö…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY3AX</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GIE26L</t>
+          <t>GDT2JM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:       - redogöra för grundläggande begrepp och metod…</t>
+          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:      - Redogöra för historik och utveckling av system för datakommunikation s…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JM</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GIE26M</t>
+          <t>GDT2JN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs skall studenten kunna:     - redogöra för grundläggande begrepp inom orga…</t>
+          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:      - Redogöra för, och värdera, hierarkiska konvergerade nätverksdesigner…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT2JN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GIE26N</t>
+          <t>GDT34Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>DTA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:         - redogöra för centrala begrepp inom kvalite…</t>
+          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva hur teknik som virtualisering, mjukvarupaketering via containerb…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GDT34Z</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GIE2L7</t>
+          <t>ET1029</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>ETA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna    - redogöra för den historiska framväxten av Lean.…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:          - Redogöra för grundläggande principer i styrteknik.    - Redogör…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ET1029</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GIE2QS</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**  Efter avslutad kurs ska studenten kunna:    - redogöra översiktligt för processorienterad ve…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om vetenskapligt arbetssätt inom naturvetenskap…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GIE2RF</t>
+          <t>FY1018</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_      Efter genomgången kurs ska studenten kunna:    - visa fördjupad kunskap inom ett valt områ…</t>
+          <t>Avvikande introfras: Studenten skall efter genomgången kurs kunna        - redogöra för termodynamikens grundbegrepp    - formulera och lösa…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FY1018</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>IE1068</t>
+          <t>GIE26L</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:    - redogöra för lämpliga sätt att problematisera,…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:       - redogöra för grundläggande begrepp och metod…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26L</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>IE1069</t>
+          <t>GIE26M</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:       - redogöra för grundläggande begrepp och metod…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs skall studenten kunna:     - redogöra för grundläggande begrepp inom orga…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26M</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IE1076</t>
+          <t>GIE26N</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,24 +1729,24 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna        - redogöra för grundläggande begrepp och föru…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:         - redogöra för centrala begrepp inom kvalite…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26N</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GIE26P</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:         - redogöra för centrala begrepp inom området…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna        - redogöra för grundläggande begrepp och föru…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE26P</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIK23M</t>
+          <t>GIE29N</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna       - redogöra för projektledarens roll och ansvar…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE29N</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIK289</t>
+          <t>GIE2L7</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:      - förklara vad begreppet objektorientering inne…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna    - redogöra för den historiska framväxten av Lean.…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2L7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIK28T</t>
+          <t>GIE2MF</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna      _Kunskap och förståelse_    - Redogöra för val av forskningsansats i r…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:    - redogöra översiktligt för utvecklingen från tra…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2MF</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GIK299</t>
+          <t>GIE2QS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
+          <t>Avvikande introfras: **Kunskap och förståelse**  Efter avslutad kurs ska studenten kunna:    - redogöra översiktligt för processorienterad ve…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2QS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GIE2RF</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:          - Förklara relevanta begrepp och terminologi inom programutveckling.…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_      Efter genomgången kurs ska studenten kunna:    - visa fördjupad kunskap inom ett valt områ…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE2RF</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GIK2AL</t>
+          <t>IE1068</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:    - redogöra för lämpliga sätt att problematisera,…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1068</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GIK2BD</t>
+          <t>IE1069</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna       - Beskriva projektstyrningsmodeller, dess f…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:       - redogöra för grundläggande begrepp och metod…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1069</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GIK2FB</t>
+          <t>IE1076</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska studenten kunna:    - Beskriva ofta förekommande begrepp inom artificiel…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse    _Efter avslutad kurs ska studenten kunna        - redogöra för grundläggande begrepp och föru…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE1076</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GIK2JX</t>
+          <t>IE2003</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:    - Redogöra för grundläggande teorier beträffand…</t>
+          <t>Avvikande introfras: De allmänna målen med examensarbetet är att ge kursdeltagarna möjligheter att utveckla sin förmåga att inom ämnet indust…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IE2003</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GIK2KM</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:         - redogöra för centrala begrepp inom området…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GIK2LF</t>
+          <t>GIK23M</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska den studerande kunna    - beskriva lagar som reglerar användning av d…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK23M</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GIK2NV</t>
+          <t>GIK289</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska studenten kunna:      - förklara vad begreppet objektorientering inne…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK289</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GIK2NX</t>
+          <t>GIK28T</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och bearbeta data…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna      _Kunskap och förståelse_    - Redogöra för val av forskningsansats i r…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK28T</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GIK2PB</t>
+          <t>GIK299</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper och färdigheter i att utveckla prog…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK299</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GIK2PF</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:          - Förklara relevanta begrepp och terminologi inom programutveckling.…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GIK2PG</t>
+          <t>GIK2AL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om principer och metoder för att designa och använda…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2AL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GIK2Q3</t>
+          <t>GIK2BD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    _   Kunskap och förståelse_    - Förklara begrepp och terminologi relaterade…</t>
+          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska den studerande kunna       - Beskriva projektstyrningsmodeller, dess f…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2BD</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GIK2QZ</t>
+          <t>GIK2FB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_     Efter avslutad kurs ska studenten kunna:       - redogöra för begrepp inom visuell kommunik…</t>
+          <t>Avvikande introfras: Kunskap och förståelse  Efter avslutad kurs ska studenten kunna:    - Beskriva ofta förekommande begrepp inom artificiel…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2FB</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GIK2UK</t>
+          <t>GIK2JX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse   Efter genomförd kurs skall studenten kunna:    - använda verktyg och funktioner som är centrala…</t>
+          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska studenten kunna:    - Redogöra för grundläggande teorier beträffand…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2JX</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GIK2XJ</t>
+          <t>GIK2KM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska studenten kunna:     - redogöra för de teoretiska grunderna inom objek…</t>
+          <t>Avvikande introfras: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att använda och utveckla mju…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2KM</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GIK2XK</t>
+          <t>GIK2LF</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:    - redogöra för centrala begrepp, metoder o…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter avslutad kurs ska den studerande kunna    - beskriva lagar som reglerar användning av d…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2LF</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GIK2XZ</t>
+          <t>GIK2NV</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:       - beskriva metoder, modeller, roller oc…</t>
+          <t>Avvikande introfras: Det övergripande målet är att studenten ska förvärva fördjupade kunskaper och färdigheter i att hantera data över ett da…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NV</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GIK32L</t>
+          <t>GIK2NX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saknar kolon</t>
+          <t>Avvikande formulering</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig kunskaper och färdigheter i att samla in och bearbeta data…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2NX</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GIK32M</t>
+          <t>GIK2PB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saknar kolon</t>
+          <t>Avvikande formulering</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig kunskap om och förståelse för systemförvaltning och test…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PB</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GIK32N</t>
+          <t>GIK2PD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saknar kolon</t>
+          <t>Avvikande formulering</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att introducera studenten till nätverk, nätverkstjänster , nätverkssäkerhet, datakommunikati…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PD</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GIK339</t>
+          <t>GIK2PF</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:    - redogöra för grundläggande begrepp inom webbutv…</t>
+          <t>Avvikande introfras: Det övergripande målet är att studenterna förvärvar fördjupade kunskaper och färdigheter inom IT-arkitektur som omfattar…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PF</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GIK347</t>
+          <t>GIK2PG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Avvikande introfras: _Kunskap och förståelse    _Efter godkänd kurs ska den studenten kunna    - använda centrala begrepp inom interaktionsde…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenter i grupp i ett systemutvecklingsprojekt planerar, analyserar, designar…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2PG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GMA28W</t>
+          <t>GIK2Q3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    _   Kunskap och förståelse_    - Förklara begrepp och terminologi relaterade…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2Q3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GIK2QZ</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - utföra numeriska beräkningar med tal i t ex decimalform, bråkform och p…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_     Efter avslutad kurs ska studenten kunna:       - redogöra för begrepp inom visuell kommunik…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2QZ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>GIK2UK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
+          <t>Avvikande introfras: Kunskap och förståelse   Efter genomförd kurs skall studenten kunna:    - använda verktyg och funktioner som är centrala…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2UK</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>GIK2V4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att introducera studenten till cybersäkerhetstrender, hotbilder vid IT-användning mot person…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2V4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AMD238</t>
+          <t>GIK2XJ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
+          <t>Avvikande introfras: Kunskap och förståelse    Efter avslutad kurs ska studenten kunna:     - redogöra för de teoretiska grunderna inom objek…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GMD2EX</t>
+          <t>GIK2XK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för olika sätt att formulera och lösa matematiska uppgifte…</t>
+          <t>Avvikande introfras: **Kunskap och förståelse**   Efter avslutad kurs ska den studerande kunna:    - redogöra för centrala begrepp, metoder o…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XK</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GMD2GU</t>
+          <t>GIK2XZ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för och problematisera, såväl muntligt som skriftligt, mat…</t>
+          <t>Avvikande introfras: **Kunskap och förståelse   **Efter avslutad kurs ska den studerande kunna:       - beskriva metoder, modeller, roller oc…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GMD2H2</t>
+          <t>GIK2YK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa kännedom om och använda matematikens grundläggande språk oc…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:    - förklara normaliseringens betydelse för en…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YK</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GMD2H4</t>
+          <t>GIK2YL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kännedom om definitioner och satser i euklidisk geometri,    - b…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:    - redogöra för metoder och modeller inom proj…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YL</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GMD2HE</t>
+          <t>GIK2YN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - identifiera och reflektera kring matematikdidaktiska begrepp, teorier…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse   _Efter godkänd kurs ska den studerande kunna:    - redogöra för grundläggande begrepp inom obj…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GMD2HF</t>
+          <t>GIK2YP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera matematikdidaktiska begrepp, teorier och perspektiv om…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_   Efter godkänd kurs ska den studerande kunna:    - förklara renderingsprocessen för HTML (Hype…</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YP</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GMD2HG</t>
+          <t>GIK2YR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,132 +2809,132 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - utifrån matematikdidaktiska ramverk, teorier och perspektiv analysera…</t>
+          <t>Avvikande introfras: Kunskap och förståelse   Efter godkänd kurs ska den studerande kunna:    - använda centrala begrepp och principer inom d…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2YR</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GMD2HH</t>
+          <t>GIK32K</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar kolon</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - identifiera och reflektera kring matematikdidaktiska begrepp, teorier…</t>
+          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32K</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GMD2HJ</t>
+          <t>GIK32L</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar kolon</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera matematikdidaktiska begrepp, teorier och perspektiv om…</t>
+          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32L</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GMD2HK</t>
+          <t>GIK32M</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar kolon</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - utifrån matematikdidaktiska ramverk, teorier och perspektiv analysera…</t>
+          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32M</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GMD2MH</t>
+          <t>GIK32N</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avvikande formulering</t>
+          <t>Saknar kolon</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - genomföra och diskutera en statistisk undersökning med relevans uti…</t>
+          <t>Saknar kolon: `Efter godkänd kurs ska studenten kunna`</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK32N</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GMD2MJ</t>
+          <t>GIK339</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,24 +2944,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - förstå begreppet funktion inklusive invers, bijektion samt monoton fu…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse_   Efter avslutad kurs ska studenten kunna:    - redogöra för grundläggande begrepp inom webbutv…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK339</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>GIK347</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - med grund i aktuella styrdokument, litteratur och undervisningsmateri…</t>
+          <t>Avvikande introfras: _Kunskap och förståelse    _Efter godkänd kurs ska den studenten kunna    - använda centrala begrepp inom interaktionsde…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK347</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GMD3GZ</t>
+          <t>IK1032</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och problematisera, såväl skriftligt som muntligt, matem…</t>
+          <t>Avvikande introfras: Målet med examensarbetet är att studenten ska förvärva fördjupade kunskaper inom examensarbetets ämnesområde genom att u…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1032</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MD1103</t>
+          <t>IK1064</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för olika vetenskapliga teorier och forskningsrön såväl nati…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande ska tillägna sig utökade kunskaper i objektorienterad programmering och m…</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1064</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>MD2023</t>
+          <t>IK1066</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva, analysera, diskutera och tillämpa differentialekvationer  a…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper och färdigheter inom ämnesområdet geno…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IK1066</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MD2024</t>
+          <t>GMA28W</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva, analysera, diskutera och tillämpa aritmetik, mängdlära,  bi…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska öka sin förmåga att förstå och använda grundläggande matematiska…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA28W</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>MD2025</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - lösa linjära ekvationssystem med matriser    - uttrycka linjer, pla…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - utföra numeriska beräkningar med tal i t ex decimalform, bråkform och p…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>MD2026</t>
+          <t>MA0011</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - lösa differentialekvationer av första ordningen, separabla differenti…</t>
+          <t>Avvikande introfras: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MT1033</t>
+          <t>MA0013</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten skall efter kursen kunna     - skriva ett program för styrning av en numeriskt styrd maskin som används inom v…</t>
+          <t>Avvikande introfras: Ett övergripande mål är att förbereda för fortsatta studier i matematik på högskolenivå.  Efter avslutad kurs skall stud…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AEG26X</t>
+          <t>MA1040</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgång av kursen ska studenten kunna:       - göra urval av komponenter för PV- och hybridsystem för elgenereri…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska utveckla sin förmåga att förstå och använda matematiska begrepp o…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1040</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AEG29N</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kursen ska studenten kunna:    - välja ändamålsenliga komponenter för nätkopplade solcellssystem,    - red…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig grundläggande teoretiska kunskaper i elementär a…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AEG2B6</t>
+          <t>AMD238</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva solljusets egenskaper före och efter passagen genom atmosfären,…</t>
+          <t>Avvikande introfras: Kursens övergripande mål är att den studerande visar sådana fördjupade ämnes- och ämnesdidaktiska kunskaper som krävs fö…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>EG1012</t>
+          <t>GMD2BH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för och problematisera, såväl skriftligt som muntligt, mat…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>EG2004</t>
+          <t>GMD2EX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för olika sätt att formulera och lösa matematiska uppgifte…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2EX</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>EG3009</t>
+          <t>GMD2GU</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - dimensionera en solvärmeanläggning    - designa solvärmesystem med a…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra för och problematisera, såväl muntligt som skriftligt, mat…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2GU</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GMD2H2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:         - ange och självständigt analysera olika sätt att anpassa och design…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:         - visa kännedom om och använda matematikens grundläggande språk oc…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>EG3019</t>
+          <t>GMD2H3</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - genomföra och diskutera en statistisk undersökning med relevans uti…</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>EG3020</t>
+          <t>GMD2H4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - visa kännedom om definitioner och satser i euklidisk geometri,    - b…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>EG3022</t>
+          <t>GMD2H5</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - förstå begreppet funktion inklusive invers, bijektion samt monoton fu…</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2H5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GEG2JP</t>
+          <t>GMD2HE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - redogöra för grundläggande begrepp som utgör förutsättningar för konstr…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - identifiera och reflektera kring matematikdidaktiska begrepp, teorier…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GEG2UE</t>
+          <t>GMD2HF</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenten skall efter genomgången kurs kunna         - kategorisera och utföra beräkningar på energianvändning i byggnad…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera matematikdidaktiska begrepp, teorier och perspektiv om…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HF</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GEG33B</t>
+          <t>GMD2HG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Studenterna ska efter avslutad kurs kunna:    - utföra en solcellsinstallation i enlighet med gällande svenskt regelverk…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - utifrån matematikdidaktiska ramverk, teorier och perspektiv analysera…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HG</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GEG39Z</t>
+          <t>GMD2HH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva skillnader mellan konventionell och omriktaransluten kraftproduk…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - identifiera och reflektera kring matematikdidaktiska begrepp, teorier…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HH</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GSQ25F</t>
+          <t>GMD2HJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - problematisera matematikdidaktiska begrepp, teorier och perspektiv om…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HJ</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GSQ25N</t>
+          <t>GMD2HK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - utifrån matematikdidaktiska ramverk, teorier och perspektiv analysera…</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2HK</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSQ2J4</t>
+          <t>GMD2MH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna: ·       - Redogöra för grundläggande begrepp och teorier inom såväl ekonomis…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - genomföra och diskutera en statistisk undersökning med relevans uti…</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MH</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GSQ2L8</t>
+          <t>GMD2MJ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:      - Redogöra för den svenska översiktliga fysiska planeringen och dess be…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - förstå begreppet funktion inklusive invers, bijektion samt monoton fu…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2MJ</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GSQ2LA</t>
+          <t>GMD2PA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om IT och digitaliseringens betydelse och användning…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - med grund i aktuella styrdokument, litteratur och undervisningsmateri…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GSQ2MC</t>
+          <t>GMD3GZ</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:      - redogöra för grundläggande begrepp inom transportsektorn relevanta fö…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för och problematisera, såväl skriftligt som muntligt, matem…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD3GZ</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSQ2PH</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3727,24 +3727,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:     - redogöra för och problematisera olika teoretiska perspektiv inom spe…</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GSQ2R5</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna       - redogöra för matematikens utveckling i stora drag, genom historien…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GSQ2VY</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - Redogöra för begrepp inom befolkningsgeografi, demografi och social geogra…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - redogöra  för olika vetenskapliga teorier och forskningsrön som beh…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSQ2WM</t>
+          <t>MD1103</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Redogöra för grundläggande geografisk informationsteknik med avseend…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - redogöra för olika vetenskapliga teorier och forskningsrön såväl nati…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GSQ2Y2</t>
+          <t>MD2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva, analysera, diskutera och tillämpa differentialekvationer  a…</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2023</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>MD2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Utföra stadsanalyser med stöd av GIS-verktyg    - Redogöra för och k…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - beskriva, analysera, diskutera och tillämpa aritmetik, mängdlära,  bi…</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2024</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GST2CL</t>
+          <t>MD2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3889,24 +3889,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter kursen skall studenten kunna:         - Sammanfatta och tolka data med hjälp av beskrivande statistik.    - Tolka…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:      - lösa linjära ekvationssystem med matriser    - uttrycka linjer, pla…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2025</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>ST1013</t>
+          <t>MD2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter kursen skall studenten kunna:       - sammanfatta och tolka data med beskrivande statistik.    - tolka datautskrif…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:    - lösa differentialekvationer av första ordningen, separabla differenti…</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD2026</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>AMI22T</t>
+          <t>GMT228</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3943,24 +3943,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - Välja rätt statistiska modeller och metoder för dataanalys av praktiska…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:          - Använda och argumentera för olika metoders användning vid identifier…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT228</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>AMI22Z</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - självständigt planera och genomföra ett maskintekniskt projektarbete in…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>AMI23A</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3997,24 +3997,24 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna       - visa förståelse för visual literacy, bestämma de grafiska elementen som…</t>
+          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:    - redogöra på principiell nivå den teoretiska grunden för finita element m…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>AMI23C</t>
+          <t>GMT2WL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:       - uttrycka praktiska problem som ett linjärprogrammeringsproblem,    -…</t>
+          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:    - skapa en CAD-modell utifrån en designidé   - redogöra för olika dataform…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2WL</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>AMI23G</t>
+          <t>MT1033</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kursen ska studenten kunna:    - Tillämpa neurala nätverk på verklig problemlösning.   - Göra jämförande…</t>
+          <t>Avvikande introfras: Studenten skall efter kursen kunna     - skriva ett program för styrning av en numeriskt styrd maskin som används inom v…</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1033</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>AMI23J</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - redogöra för grundbegreppen spänning och töjning.    - redogöra för…</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>AMI23K</t>
+          <t>MT1068</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna       -  Redogöra för och visa förståelse för vikten av olika typer av data och…</t>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:      - Identifiera kundkrav    - Specificera produktegenskaper utgående från ku…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1068</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>AMI23L</t>
+          <t>MT1074</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,24 +4132,24 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs kommer studenten att kunna:      - Manipulera rumslig data i både R och GIS   - Använda programvaran…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall tillägna sig kännedom om och förmåga till analys av de viktigas…</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1074</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>AMI27V</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4159,24 +4159,24 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - göra plåtutbredning av tunnväggiga konstruktioner     - använda svetsmo…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>AMI295</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna    - tillämpa och diskutera olika resultatindikatorer för att utvärdera inves…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:         - redogöra för olika algebraiska system, modulär aritmetik och polynom…</t>
+          <t>Avvikande introfras: Efter avslutad kurs, ska studenten kunna:       - Redogöra för grundläggande elteknik, termodynamik och mättteknik som k…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GMI24H</t>
+          <t>AEG233</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4240,24 +4240,24 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - Använda olika typer av datastrukturer samt visa förståelse för der…</t>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna       - analysera och diskutera de fysiska processer som styr utbytet av olik…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG233</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GMI26H</t>
+          <t>AEG26X</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - Förklara kryptografiska begrepp    - Jämföra symmetriska och asymmetris…</t>
+          <t>Avvikande introfras: Efter genomgång av kursen ska studenten kunna:       - göra urval av komponenter för PV- och hybridsystem för elgenereri…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GMI2C8</t>
+          <t>AEG29N</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa…</t>
+          <t>Avvikande introfras: Efter godkänd kursen ska studenten kunna:    - välja ändamålsenliga komponenter för nätkopplade solcellssystem,    - red…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG29N</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GMI2J3</t>
+          <t>AEG2B6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,24 +4321,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna       - beskriva mjukvarutestningens roll i systemutvecklingsprocessen.…</t>
+          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva solljusets egenskaper före och efter passagen genom atmosfären,…</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2B6</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GMI2MD</t>
+          <t>BEG222</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,24 +4348,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad utbildning ska den studerande kunna:      Kunskap och Förståelse      - Förklara innebörden av IoT- (Inte…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall ha nått en förtrogenhet med rådande forsknings- och utbildnings…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BEG222</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GMI2NW</t>
+          <t>EG1012</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest…</t>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig kunskap och förståelse för grunder i strömningsl…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>MI4001</t>
+          <t>EG2004</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,44 +4402,1610 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna      - Analysera styrkor och begränsningar hos verktyg och tekniker som kan anvä…</t>
+          <t>Avvikande introfras: Det övergripande målet med examensarbetet är att studenten inom givna ramar ska utföra ett arbete av utvecklingskaraktär…</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG2004</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>EG3007</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - analysera och diskutera de fysikaliska processer som styr utbytet av en…</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>EG3009</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - dimensionera en solvärmeanläggning    - designa solvärmesystem med a…</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>EG3012</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:        - förklara de grundläggande principerna för tekniska system vid gener…</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:         - ange och självständigt analysera olika sätt att anpassa och design…</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs skall studenten kunna         - visa på kunskap om solljusets egenskaper före och efter passagen…</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>EG3017</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs, ska studenten kunna:       - redogöra för det aktuella företagets organisation och verksamhet    -…</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>EG3018</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs, ska studenten kunna:       - redogöra för det aktuella företagets organisation och verksamhet    -…</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>EG3019</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenterna skall tillägna sig insikt i miljömässig och ekonomisk hållbarhet i…</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>EG3020</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet energitekni…</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>EG3022</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Målet med examensarbetet är att studenten ska kunna tillämpa fördjupade kunskaper inom huvudområdet solenergiteknik geno…</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Målet med examensarbetet är att studenten ska kunna tillämpa och väsentligen fördjupa sina kunskaper inom solenergitekni…</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>GEG26J</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:         - Planera, skapa, och leverera tydliga vetenskapliga presentationer…</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GEG2JP</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - redogöra för grundläggande begrepp som utgör förutsättningar för konstr…</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GEG2UE</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Studenten skall efter genomgången kurs kunna         - kategorisera och utföra beräkningar på energianvändning i byggnad…</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GEG2UL</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Den studerande ska efter avslutad kurs kunna:     - redogöra för koncept och teknologier för elkraftgenerering med utgån…</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GEG33B</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Studenterna ska efter avslutad kurs kunna:    - utföra en solcellsinstallation i enlighet med gällande svenskt regelverk…</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG33B</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GEG39Z</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs skall studenten kunna:    - beskriva skillnader mellan konventionell och omriktaransluten kraftproduk…</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GEG3FY</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter godkänd kurs, ska studenten kunna:    - redogöra för den aktuella organisationens verksamhet och struktur    - gen…</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3FY</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23J</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall tillämpa och fördjupa kunskaper och tekniker i databashantering…</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23K</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Redogöra för fördjupade planeringteoretiska och diskursiva perspekti…</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25F</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att introducera form och gestaltning av byggnader och stadsmiljöer med fokus på verktyg för…</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25J</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25K</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Utföra stadsanalyser med stöd av GIS-verktyg    - Redogöra för och k…</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25N</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Examensarbetets övergripande mål är att studenten ska tillämpa och fördjupa tidigare inhämtade kunskaper och färdigheter…</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2DH</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Skapa tematiska kartor med hjälp av GIS    - Redogöra för projektion…</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2DH</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2H7</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursen syftar till att öka förståelsen för den gestaltade livsmiljöns betydelse för ett gott vardagsliv och hur den hant…</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2H7</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2J4</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna: ·       - Redogöra för grundläggande begrepp och teorier inom såväl ekonomis…</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2L8</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:      - Redogöra för den svenska översiktliga fysiska planeringen och dess be…</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2L9</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:    - Redogöra för grundläggande geografisk informationsteknik med avseende p…</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2LA</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskap om IT och digitaliseringens betydelse och användning…</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2MC</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:      - redogöra för grundläggande begrepp inom transportsektorn relevanta fö…</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2MC</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2PH</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska tillägna sig fördjupade kunskaper inom fysisk planering med tyngd…</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2R5</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig färdigheter inom kvantitativa analyser av urbana och r…</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2VY</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:    - Redogöra för begrepp inom befolkningsgeografi, demografi och social geogra…</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2VY</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2WM</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Redogöra för grundläggande geografisk informationsteknik med avseend…</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2WM</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2Y2</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskaplig metod. Efter genomgånge…</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>GSQ33N</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter genomgången kurs ska studenten kunna:       - Utföra stadsanalyser med stöd av GIS-verktyg    - Redogöra för och k…</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>SQ1003</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska skaffa sig förtrogenhet inom vetenskapligt metod. Efter genomgång…</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SQ1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>GST2CL</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter kursen skall studenten kunna:         - Sammanfatta och tolka data med hjälp av beskrivande statistik.    - Tolka…</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GST2CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>ST1013</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>STA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter kursen skall studenten kunna:       - sammanfatta och tolka data med beskrivande statistik.    - tolka datautskrif…</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ST1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>AMI22T</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - Välja rätt statistiska modeller och metoder för dataanalys av praktiska…</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22T</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>AMI22Z</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande syftet med kursen är att studenten skall utveckla kunskap om riskhändelser och -processer med målet att…</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI22Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>AMI23A</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna       - visa förståelse för visual literacy, bestämma de grafiska elementen som…</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23A</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>AMI23C</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs skall studenten kunna:       - uttrycka praktiska problem som ett linjärprogrammeringsproblem,    -…</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>AMI23G</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kursen ska studenten kunna:    - Tillämpa neurala nätverk på verklig problemlösning.   - Göra jämförande…</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>AMI23J</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ges möjlighet att i en professionell miljö tillämpa sina kunskaper oc…</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23J</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>AMI23K</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna       -  Redogöra för och visa förståelse för vikten av olika typer av data och…</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23K</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>AMI23L</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs kommer studenten att kunna:      - Manipulera rumslig data i både R och GIS   - Använda programvaran…</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI23L</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>AMI27V</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten skall utveckla förståelse för vad som förhindrar rationellt och datad…</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI27V</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>AMI295</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Kursens övergripande mål är att studenten ska tillägna sig kunskaper om begrepp och metoder av Business Intelligence (BI…</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMI295</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>GMI23G</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:         - redogöra för olika algebraiska system, modulär aritmetik och polynom…</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>GMI24H</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna:       - Använda olika typer av datastrukturer samt visa förståelse för der…</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI24H</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>GMI26H</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna:       - Förklara kryptografiska begrepp    - Jämföra symmetriska och asymmetris…</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI26H</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>GMI2C8</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Examensarbetet är det avslutande tillfället för studenten att tillämpa grundläggande kunskaper och ytterligare fördjupa…</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>GMI2J3</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska den studerande kunna       - beskriva mjukvarutestningens roll i systemutvecklingsprocessen.…</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>GMI2MD</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad utbildning ska den studerande kunna:      Kunskap och Förståelse      - Förklara innebörden av IoT- (Inte…</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>GMI2NW</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Det övergripande målet med kursen är att studenten ska behandla aktiviteter relaterade till automatiska programvarutest…</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2NW</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>MI4001</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna      - Analysera styrkor och begränsningar hos verktyg och tekniker som kan anvä…</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
           <t>MI4002</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Avvikande formulering</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Avvikande formulering</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
         <is>
           <t>Avvikande introfras: Efter avslutad kurs ska studenten kunna         - Analysera styrkor och begränsningar hos verktyg och tekniker som kan a…</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MI4002</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E148"/>
+  <autoFilter ref="A1:E206"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -4735,6 +6301,122 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$206</definedName>

--- a/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens lärandemål.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Frasningskonsistens lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Frasningskonsistens lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Frasningskonsistens lärandemål'!$A$1:$E$206</definedName>
